--- a/www/terminologies/ValueSet-JDV-J238-TypeOffre-ROR.xlsx
+++ b/www/terminologies/ValueSet-JDV-J238-TypeOffre-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="607">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="621">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20251222120000</t>
+    <t>20260223120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-22T12:00:00+01:00</t>
+    <t>2026-02-23T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1728,7 +1728,7 @@
     <t>279</t>
   </si>
   <si>
-    <t>Equipe mobile de psychiatrie de l'Enfant et de l'Adolescent</t>
+    <t>Equipe Mobile de Psychiatrie de l’Enfant et de l’Adolescent (EMPEA)</t>
   </si>
   <si>
     <t>280</t>
@@ -1825,6 +1825,48 @@
   </si>
   <si>
     <t>Permanence d'Accès aux Soins de Santé (PASS)</t>
+  </si>
+  <si>
+    <t>296</t>
+  </si>
+  <si>
+    <t>Groupe d’Entraide Mutuelle (GEM)</t>
+  </si>
+  <si>
+    <t>297</t>
+  </si>
+  <si>
+    <t>Centre ressource IntimAgir</t>
+  </si>
+  <si>
+    <t>298</t>
+  </si>
+  <si>
+    <t>Dispositif sanitaire dédié à la prise en charge des femmes victimes de violences (Maison des Femmes Santé)</t>
+  </si>
+  <si>
+    <t>299</t>
+  </si>
+  <si>
+    <t>Equipe de Diagnostic de Proximité – Autisme (PDAP, EDAP)</t>
+  </si>
+  <si>
+    <t>300</t>
+  </si>
+  <si>
+    <t>Equipe Mobile de Psychiatrie Périnatale</t>
+  </si>
+  <si>
+    <t>301</t>
+  </si>
+  <si>
+    <t>Unité d'urgences psychiatriques</t>
+  </si>
+  <si>
+    <t>302</t>
+  </si>
+  <si>
+    <t>Centre d’Accueil et de Crise (CAC)</t>
   </si>
   <si>
     <t/>
@@ -2095,7 +2137,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B291"/>
+  <dimension ref="A1:B298"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -4419,15 +4461,71 @@
         <v>604</v>
       </c>
       <c r="B290" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B291" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="B292" t="s" s="2">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="B293" t="s" s="2">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="B294" t="s" s="2">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="B295" t="s" s="2">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="B296" t="s" s="2">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="B297" t="s" s="2">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="B298" t="s" s="2">
+        <v>620</v>
       </c>
     </row>
   </sheetData>

--- a/www/terminologies/ValueSet-JDV-J238-TypeOffre-ROR.xlsx
+++ b/www/terminologies/ValueSet-JDV-J238-TypeOffre-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="621">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="623">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260223120000</t>
+    <t>20260330120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T12:00:00+01:00</t>
+    <t>2026-03-30T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -102,13 +102,13 @@
     <t>01</t>
   </si>
   <si>
-    <t>Appartement thérapeutique</t>
+    <t>Appartement thérapeutique en psychiatrie</t>
   </si>
   <si>
     <t>02</t>
   </si>
   <si>
-    <t>Atelier thérapeutique</t>
+    <t>Atelier thérapeutique en psychiatrie</t>
   </si>
   <si>
     <t>03</t>
@@ -174,7 +174,7 @@
     <t>13</t>
   </si>
   <si>
-    <t>Service d'Accueil Familial Thérapeutique</t>
+    <t>Service d'Accueil Familial Thérapeutique en psychiatrie</t>
   </si>
   <si>
     <t>14</t>
@@ -216,7 +216,7 @@
     <t>20</t>
   </si>
   <si>
-    <t>Unité d'urgences</t>
+    <t>Unité d'urgences polyvalentes</t>
   </si>
   <si>
     <t>21</t>
@@ -486,7 +486,7 @@
     <t>66</t>
   </si>
   <si>
-    <t>Equipe Relai Handicap rare</t>
+    <t>Equipe Relais Handicaps Rares (ERHR)</t>
   </si>
   <si>
     <t>67</t>
@@ -951,12 +951,6 @@
     <t>Unité de prise en charge des brûlés</t>
   </si>
   <si>
-    <t>147</t>
-  </si>
-  <si>
-    <t>Unité de sevrage complexe</t>
-  </si>
-  <si>
     <t>148</t>
   </si>
   <si>
@@ -1617,12 +1611,6 @@
     <t>Point d'information local dédié aux personnes âgées</t>
   </si>
   <si>
-    <t>261</t>
-  </si>
-  <si>
-    <t>Accueil familial pour personne âgée</t>
-  </si>
-  <si>
     <t>262</t>
   </si>
   <si>
@@ -1851,12 +1839,6 @@
     <t>Equipe de Diagnostic de Proximité – Autisme (PDAP, EDAP)</t>
   </si>
   <si>
-    <t>300</t>
-  </si>
-  <si>
-    <t>Equipe Mobile de Psychiatrie Périnatale</t>
-  </si>
-  <si>
     <t>301</t>
   </si>
   <si>
@@ -1867,6 +1849,30 @@
   </si>
   <si>
     <t>Centre d’Accueil et de Crise (CAC)</t>
+  </si>
+  <si>
+    <t>303</t>
+  </si>
+  <si>
+    <t>Cabinet de ville infirmier en pratique avancée en pathologies chroniques stabilisées</t>
+  </si>
+  <si>
+    <t>304</t>
+  </si>
+  <si>
+    <t>Cabinet de ville infirmier en pratique avancée en oncologie et hémato-oncologie</t>
+  </si>
+  <si>
+    <t>305</t>
+  </si>
+  <si>
+    <t>Cabinet de ville infirmier en pratique avancée en maladie rénale chronique</t>
+  </si>
+  <si>
+    <t>306</t>
+  </si>
+  <si>
+    <t>Cabinet de ville infirmier en pratique avancée en santé mentale</t>
   </si>
   <si>
     <t/>
@@ -2137,7 +2143,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B298"/>
+  <dimension ref="A1:B299"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -4517,15 +4523,23 @@
         <v>618</v>
       </c>
       <c r="B297" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B298" t="s" s="2">
         <v>620</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="B299" t="s" s="2">
+        <v>622</v>
       </c>
     </row>
   </sheetData>

--- a/www/terminologies/ValueSet-JDV-J238-TypeOffre-ROR.xlsx
+++ b/www/terminologies/ValueSet-JDV-J238-TypeOffre-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="623">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="637">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260330120000</t>
+    <t>20260505120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T12:00:00+01:00</t>
+    <t>2026-05-05T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -216,7 +216,7 @@
     <t>20</t>
   </si>
   <si>
-    <t>Unité d'urgences polyvalentes</t>
+    <t>Structure des urgences polyvalentes 24h/24 7j/7</t>
   </si>
   <si>
     <t>21</t>
@@ -948,7 +948,7 @@
     <t>146</t>
   </si>
   <si>
-    <t>Unité de prise en charge des brûlés</t>
+    <t>Unité hospitalière de brûlologie</t>
   </si>
   <si>
     <t>148</t>
@@ -1873,6 +1873,48 @@
   </si>
   <si>
     <t>Cabinet de ville infirmier en pratique avancée en santé mentale</t>
+  </si>
+  <si>
+    <t>307</t>
+  </si>
+  <si>
+    <t>Unité d’Education Thérapeutique du Patient (ETP)</t>
+  </si>
+  <si>
+    <t>308</t>
+  </si>
+  <si>
+    <t>Unité de réanimation des brûlés</t>
+  </si>
+  <si>
+    <t>309</t>
+  </si>
+  <si>
+    <t>Unité Sanitaire en Milieu Pénitentiaire (USMP, ex UCSA)</t>
+  </si>
+  <si>
+    <t>310</t>
+  </si>
+  <si>
+    <t>Lactarium</t>
+  </si>
+  <si>
+    <t>311</t>
+  </si>
+  <si>
+    <t>Structure des urgences pédiatriques</t>
+  </si>
+  <si>
+    <t>312</t>
+  </si>
+  <si>
+    <t>Pharmacie d'officine (dont mutualiste)</t>
+  </si>
+  <si>
+    <t>313</t>
+  </si>
+  <si>
+    <t>Antennes des urgences</t>
   </si>
   <si>
     <t/>
@@ -2143,7 +2185,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B299"/>
+  <dimension ref="A1:B306"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -4531,15 +4573,71 @@
         <v>620</v>
       </c>
       <c r="B298" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B299" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="B300" t="s" s="2">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="B301" t="s" s="2">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="B302" t="s" s="2">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="B303" t="s" s="2">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="B304" t="s" s="2">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="B305" t="s" s="2">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="B306" t="s" s="2">
+        <v>636</v>
       </c>
     </row>
   </sheetData>

--- a/www/terminologies/ValueSet-JDV-J238-TypeOffre-ROR.xlsx
+++ b/www/terminologies/ValueSet-JDV-J238-TypeOffre-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="637">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="629">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260505120000</t>
+    <t>20260629120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-05T12:00:00+01:00</t>
+    <t>2026-06-29T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1563,12 +1563,6 @@
     <t>Centre Périnatal de Proximité (CPP)</t>
   </si>
   <si>
-    <t>252</t>
-  </si>
-  <si>
-    <t>Equipes Mobiles de Soins Palliatifs (EMSP)</t>
-  </si>
-  <si>
     <t>253</t>
   </si>
   <si>
@@ -1627,24 +1621,6 @@
   </si>
   <si>
     <t>Unité de soins intensifs spécialisés hématologie (USIH)</t>
-  </si>
-  <si>
-    <t>265</t>
-  </si>
-  <si>
-    <t>Equipe mobile d'algologie</t>
-  </si>
-  <si>
-    <t>266</t>
-  </si>
-  <si>
-    <t>Equipe mobile de gériatrie (EMG)</t>
-  </si>
-  <si>
-    <t>267</t>
-  </si>
-  <si>
-    <t>Equipe mobile d'endocrinologie, diabétologie, métabolisme et nutrition</t>
   </si>
   <si>
     <t>268</t>
@@ -2185,7 +2161,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B306"/>
+  <dimension ref="A1:B302"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -4597,47 +4573,15 @@
         <v>626</v>
       </c>
       <c r="B301" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="B302" t="s" s="2">
         <v>628</v>
-      </c>
-      <c r="B302" t="s" s="2">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="303">
-      <c r="A303" t="s" s="2">
-        <v>630</v>
-      </c>
-      <c r="B303" t="s" s="2">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="304">
-      <c r="A304" t="s" s="2">
-        <v>632</v>
-      </c>
-      <c r="B304" t="s" s="2">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" t="s" s="2">
-        <v>634</v>
-      </c>
-      <c r="B305" t="s" s="2">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="306">
-      <c r="A306" t="s" s="2">
-        <v>635</v>
-      </c>
-      <c r="B306" t="s" s="2">
-        <v>636</v>
       </c>
     </row>
   </sheetData>

--- a/www/terminologies/ValueSet-JDV-J238-TypeOffre-ROR.xlsx
+++ b/www/terminologies/ValueSet-JDV-J238-TypeOffre-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="629">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="637">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260629120000</t>
+    <t>20260505120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:00:00+01:00</t>
+    <t>2026-05-05T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1563,6 +1563,12 @@
     <t>Centre Périnatal de Proximité (CPP)</t>
   </si>
   <si>
+    <t>252</t>
+  </si>
+  <si>
+    <t>Equipes Mobiles de Soins Palliatifs (EMSP)</t>
+  </si>
+  <si>
     <t>253</t>
   </si>
   <si>
@@ -1621,6 +1627,24 @@
   </si>
   <si>
     <t>Unité de soins intensifs spécialisés hématologie (USIH)</t>
+  </si>
+  <si>
+    <t>265</t>
+  </si>
+  <si>
+    <t>Equipe mobile d'algologie</t>
+  </si>
+  <si>
+    <t>266</t>
+  </si>
+  <si>
+    <t>Equipe mobile de gériatrie (EMG)</t>
+  </si>
+  <si>
+    <t>267</t>
+  </si>
+  <si>
+    <t>Equipe mobile d'endocrinologie, diabétologie, métabolisme et nutrition</t>
   </si>
   <si>
     <t>268</t>
@@ -2161,7 +2185,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B302"/>
+  <dimension ref="A1:B306"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -4573,15 +4597,47 @@
         <v>626</v>
       </c>
       <c r="B301" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B302" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="B303" t="s" s="2">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="B304" t="s" s="2">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="B305" t="s" s="2">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="B306" t="s" s="2">
+        <v>636</v>
       </c>
     </row>
   </sheetData>

--- a/www/terminologies/ValueSet-JDV-J238-TypeOffre-ROR.xlsx
+++ b/www/terminologies/ValueSet-JDV-J238-TypeOffre-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="629">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="645" uniqueCount="643">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260629120000</t>
+    <t>20260730120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:00:00+01:00</t>
+    <t>2026-07-30T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1302,7 +1302,7 @@
     <t>206</t>
   </si>
   <si>
-    <t>Cabinet de ville de pédicure-podologie</t>
+    <t>Cabinet de ville de pédicurie-podologie</t>
   </si>
   <si>
     <t>207</t>
@@ -1890,7 +1890,49 @@
     <t>313</t>
   </si>
   <si>
-    <t>Antennes des urgences</t>
+    <t>Antenne des urgences</t>
+  </si>
+  <si>
+    <t>314</t>
+  </si>
+  <si>
+    <t>Centre de Prise en Charge des Auteurs et/ou Auteures de violences conjugales (CPCA)</t>
+  </si>
+  <si>
+    <t>315</t>
+  </si>
+  <si>
+    <t>Equipe de Soins Spécialisés (ESS)</t>
+  </si>
+  <si>
+    <t>316</t>
+  </si>
+  <si>
+    <t>Société de téléconsultation</t>
+  </si>
+  <si>
+    <t>317</t>
+  </si>
+  <si>
+    <t>Unité hospitalière de soins de support</t>
+  </si>
+  <si>
+    <t>318</t>
+  </si>
+  <si>
+    <t>Groupe plaies et cicatrisation (dont équipe mobile)</t>
+  </si>
+  <si>
+    <t>319</t>
+  </si>
+  <si>
+    <t>Centre du sommeil</t>
+  </si>
+  <si>
+    <t>320</t>
+  </si>
+  <si>
+    <t>Offre de relayage au domicile</t>
   </si>
   <si>
     <t/>
@@ -2161,7 +2203,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B302"/>
+  <dimension ref="A1:B309"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -4573,15 +4615,71 @@
         <v>626</v>
       </c>
       <c r="B301" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B302" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="B303" t="s" s="2">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="B304" t="s" s="2">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="B305" t="s" s="2">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="B306" t="s" s="2">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="B307" t="s" s="2">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="B308" t="s" s="2">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="B309" t="s" s="2">
+        <v>642</v>
       </c>
     </row>
   </sheetData>
